--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -723,7 +723,7 @@
     <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis|20260716085853</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -1387,7 +1387,7 @@
     <t>Task.input:typeMotorisation.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20260716085852</t>
   </si>
   <si>
     <t>Task.input:natureTransport</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
